--- a/tester/lt/tuan3/lab4.xlsx
+++ b/tester/lt/tuan3/lab4.xlsx
@@ -1309,14 +1309,30 @@
           <t>Giảm 15%</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr"/>
-      <c r="C36" s="27" t="inlineStr"/>
-      <c r="D36" s="27" t="inlineStr"/>
-      <c r="E36" s="27" t="inlineStr"/>
-      <c r="F36" s="27" t="inlineStr"/>
-      <c r="G36" s="27" t="inlineStr"/>
-      <c r="H36" s="27" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr"/>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
+      <c r="H36" s="27" t="n"/>
+      <c r="I36" s="27" t="n"/>
       <c r="J36" s="27" t="n"/>
     </row>
     <row r="37">
@@ -1325,14 +1341,18 @@
           <t>Giảm 10%</t>
         </is>
       </c>
-      <c r="B37" s="27" t="inlineStr"/>
-      <c r="C37" s="27" t="inlineStr"/>
-      <c r="D37" s="27" t="inlineStr"/>
-      <c r="E37" s="27" t="inlineStr"/>
-      <c r="F37" s="27" t="inlineStr"/>
-      <c r="G37" s="27" t="inlineStr"/>
-      <c r="H37" s="27" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr"/>
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
       <c r="J37" s="27" t="n"/>
     </row>
     <row r="38">
@@ -1341,14 +1361,22 @@
           <t>Giảm 20%</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr"/>
-      <c r="C38" s="27" t="inlineStr"/>
-      <c r="D38" s="27" t="inlineStr"/>
-      <c r="E38" s="27" t="inlineStr"/>
-      <c r="F38" s="27" t="inlineStr"/>
-      <c r="G38" s="27" t="inlineStr"/>
-      <c r="H38" s="27" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr"/>
+      <c r="B38" s="27" t="n"/>
+      <c r="C38" s="27" t="n"/>
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G38" s="27" t="n"/>
+      <c r="H38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" s="27" t="n"/>
       <c r="J38" s="27" t="n"/>
     </row>
     <row r="39">
@@ -1357,14 +1385,18 @@
           <t>Không giảm</t>
         </is>
       </c>
-      <c r="B39" s="27" t="inlineStr"/>
-      <c r="C39" s="27" t="inlineStr"/>
-      <c r="D39" s="27" t="inlineStr"/>
-      <c r="E39" s="27" t="inlineStr"/>
-      <c r="F39" s="27" t="inlineStr"/>
-      <c r="G39" s="27" t="inlineStr"/>
-      <c r="H39" s="27" t="inlineStr"/>
-      <c r="I39" s="27" t="inlineStr"/>
+      <c r="B39" s="27" t="n"/>
+      <c r="C39" s="27" t="n"/>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
+      <c r="H39" s="27" t="n"/>
+      <c r="I39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J39" s="27" t="n"/>
     </row>
     <row r="40">
@@ -1373,14 +1405,46 @@
           <t>Output</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="8" t="inlineStr"/>
-      <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="J40" s="13" t="n"/>
     </row>
     <row r="41">
@@ -1413,7 +1477,7 @@
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>Ghi quy tắc rút gọn theo đề (ưu đãi cao nhất / cộng dồn / ràng buộc không áp dụng...).</t>
+          <t>Quy tắc: Phiếu 20% chỉ áp dụng khi KH không phải KH mới; ưu tiên áp dụng: Phiếu 20% (nếu hợp lệ) &gt; KH mới 15% &gt; KH thân thiết 10% &gt; Không giảm.</t>
         </is>
       </c>
       <c r="B43" s="24" t="n"/>
@@ -1493,22 +1557,22 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F47" s="13" t="n"/>
@@ -1525,22 +1589,22 @@
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F48" s="13" t="n"/>
@@ -1557,22 +1621,22 @@
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F49" s="13" t="n"/>
@@ -1603,10 +1667,14 @@
           <t>Giảm 15%</t>
         </is>
       </c>
-      <c r="B51" s="27" t="inlineStr"/>
-      <c r="C51" s="27" t="inlineStr"/>
-      <c r="D51" s="27" t="inlineStr"/>
-      <c r="E51" s="27" t="inlineStr"/>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C51" s="27" t="n"/>
+      <c r="D51" s="27" t="n"/>
+      <c r="E51" s="27" t="n"/>
       <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
       <c r="H51" s="27" t="n"/>
@@ -1619,10 +1687,14 @@
           <t>Giảm 10%</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr"/>
-      <c r="C52" s="27" t="inlineStr"/>
-      <c r="D52" s="27" t="inlineStr"/>
-      <c r="E52" s="27" t="inlineStr"/>
+      <c r="B52" s="27" t="n"/>
+      <c r="C52" s="27" t="n"/>
+      <c r="D52" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E52" s="27" t="n"/>
       <c r="F52" s="27" t="n"/>
       <c r="G52" s="27" t="n"/>
       <c r="H52" s="27" t="n"/>
@@ -1635,10 +1707,14 @@
           <t>Giảm 20%</t>
         </is>
       </c>
-      <c r="B53" s="27" t="inlineStr"/>
-      <c r="C53" s="27" t="inlineStr"/>
-      <c r="D53" s="27" t="inlineStr"/>
-      <c r="E53" s="27" t="inlineStr"/>
+      <c r="B53" s="27" t="n"/>
+      <c r="C53" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="27" t="n"/>
       <c r="F53" s="27" t="n"/>
       <c r="G53" s="27" t="n"/>
       <c r="H53" s="27" t="n"/>
@@ -1651,10 +1727,14 @@
           <t>Không giảm</t>
         </is>
       </c>
-      <c r="B54" s="27" t="inlineStr"/>
-      <c r="C54" s="27" t="inlineStr"/>
-      <c r="D54" s="27" t="inlineStr"/>
-      <c r="E54" s="27" t="inlineStr"/>
+      <c r="B54" s="27" t="n"/>
+      <c r="C54" s="27" t="n"/>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F54" s="27" t="n"/>
       <c r="G54" s="27" t="n"/>
       <c r="H54" s="27" t="n"/>
@@ -1667,10 +1747,26 @@
           <t>Output</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr"/>
-      <c r="C55" s="8" t="inlineStr"/>
-      <c r="D55" s="8" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="F55" s="13" t="n"/>
       <c r="G55" s="13" t="n"/>
       <c r="H55" s="13" t="n"/>
@@ -1910,7 +2006,7 @@
     <row r="67">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>TC1:</t>
+          <t>TC1: KH mới=T, thân thiết=F, phiếu=F → Giảm 15% (R1)</t>
         </is>
       </c>
       <c r="B67" s="24" t="n"/>
@@ -1926,7 +2022,7 @@
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>TC2:</t>
+          <t>TC2: KH mới=T, thân thiết=F, phiếu=T → Phiếu không áp dụng, Giảm 15% (R1)</t>
         </is>
       </c>
       <c r="B68" s="24" t="n"/>
@@ -1942,7 +2038,7 @@
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>TC3:</t>
+          <t>TC3: KH mới=F, thân thiết=T, phiếu=T → Giảm 20% (R2)</t>
         </is>
       </c>
       <c r="B69" s="24" t="n"/>
@@ -1958,7 +2054,7 @@
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>TC4:</t>
+          <t>TC4: KH mới=F, thân thiết=T, phiếu=F → Giảm 10% (R3)</t>
         </is>
       </c>
       <c r="B70" s="24" t="n"/>
@@ -1974,7 +2070,7 @@
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>TC5:</t>
+          <t>TC5: KH mới=F, thân thiết=F, phiếu=F → Không giảm (R4)</t>
         </is>
       </c>
       <c r="B71" s="24" t="n"/>
@@ -2730,14 +2826,18 @@
           <t>Giảm 5%</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr"/>
-      <c r="C36" s="27" t="inlineStr"/>
-      <c r="D36" s="27" t="inlineStr"/>
-      <c r="E36" s="27" t="inlineStr"/>
-      <c r="F36" s="27" t="inlineStr"/>
-      <c r="G36" s="27" t="inlineStr"/>
-      <c r="H36" s="27" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr"/>
+      <c r="B36" s="27" t="n"/>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
+      <c r="H36" s="27" t="n"/>
+      <c r="I36" s="27" t="n"/>
       <c r="J36" s="27" t="n"/>
     </row>
     <row r="37">
@@ -2746,14 +2846,22 @@
           <t>Giảm 10%</t>
         </is>
       </c>
-      <c r="B37" s="27" t="inlineStr"/>
-      <c r="C37" s="27" t="inlineStr"/>
-      <c r="D37" s="27" t="inlineStr"/>
-      <c r="E37" s="27" t="inlineStr"/>
-      <c r="F37" s="27" t="inlineStr"/>
-      <c r="G37" s="27" t="inlineStr"/>
-      <c r="H37" s="27" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr"/>
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
       <c r="J37" s="27" t="n"/>
     </row>
     <row r="38">
@@ -2762,14 +2870,30 @@
           <t>Giảm 25%</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr"/>
-      <c r="C38" s="27" t="inlineStr"/>
-      <c r="D38" s="27" t="inlineStr"/>
-      <c r="E38" s="27" t="inlineStr"/>
-      <c r="F38" s="27" t="inlineStr"/>
-      <c r="G38" s="27" t="inlineStr"/>
-      <c r="H38" s="27" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr"/>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="n"/>
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G38" s="27" t="n"/>
+      <c r="H38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" s="27" t="n"/>
       <c r="J38" s="27" t="n"/>
     </row>
     <row r="39">
@@ -2778,14 +2902,18 @@
           <t>Không giảm</t>
         </is>
       </c>
-      <c r="B39" s="27" t="inlineStr"/>
-      <c r="C39" s="27" t="inlineStr"/>
-      <c r="D39" s="27" t="inlineStr"/>
-      <c r="E39" s="27" t="inlineStr"/>
-      <c r="F39" s="27" t="inlineStr"/>
-      <c r="G39" s="27" t="inlineStr"/>
-      <c r="H39" s="27" t="inlineStr"/>
-      <c r="I39" s="27" t="inlineStr"/>
+      <c r="B39" s="27" t="n"/>
+      <c r="C39" s="27" t="n"/>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
+      <c r="H39" s="27" t="n"/>
+      <c r="I39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J39" s="27" t="n"/>
     </row>
     <row r="40">
@@ -2794,14 +2922,46 @@
           <t>Output</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="8" t="inlineStr"/>
-      <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="J40" s="13" t="n"/>
     </row>
     <row r="41">
@@ -2834,7 +2994,7 @@
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>Ghi quy tắc rút gọn theo đề (ưu đãi cao nhất / cộng dồn / ràng buộc không áp dụng...).</t>
+          <t>Quy tắc: Không áp dụng đồng thời; chọn ưu đãi cao nhất theo thứ tự: Voucher 25% &gt; Thẻ tích điểm 10% &gt; Sinh nhật 5% &gt; Không giảm.</t>
         </is>
       </c>
       <c r="B43" s="24" t="n"/>
@@ -2914,22 +3074,22 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F47" s="13" t="n"/>
@@ -2946,22 +3106,22 @@
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F48" s="13" t="n"/>
@@ -2978,22 +3138,22 @@
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F49" s="13" t="n"/>
@@ -3024,10 +3184,14 @@
           <t>Giảm 5%</t>
         </is>
       </c>
-      <c r="B51" s="27" t="inlineStr"/>
-      <c r="C51" s="27" t="inlineStr"/>
-      <c r="D51" s="27" t="inlineStr"/>
-      <c r="E51" s="27" t="inlineStr"/>
+      <c r="B51" s="27" t="n"/>
+      <c r="C51" s="27" t="n"/>
+      <c r="D51" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E51" s="27" t="n"/>
       <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
       <c r="H51" s="27" t="n"/>
@@ -3040,10 +3204,14 @@
           <t>Giảm 10%</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr"/>
-      <c r="C52" s="27" t="inlineStr"/>
-      <c r="D52" s="27" t="inlineStr"/>
-      <c r="E52" s="27" t="inlineStr"/>
+      <c r="B52" s="27" t="n"/>
+      <c r="C52" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D52" s="27" t="n"/>
+      <c r="E52" s="27" t="n"/>
       <c r="F52" s="27" t="n"/>
       <c r="G52" s="27" t="n"/>
       <c r="H52" s="27" t="n"/>
@@ -3056,10 +3224,14 @@
           <t>Giảm 25%</t>
         </is>
       </c>
-      <c r="B53" s="27" t="inlineStr"/>
-      <c r="C53" s="27" t="inlineStr"/>
-      <c r="D53" s="27" t="inlineStr"/>
-      <c r="E53" s="27" t="inlineStr"/>
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C53" s="27" t="n"/>
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="27" t="n"/>
       <c r="F53" s="27" t="n"/>
       <c r="G53" s="27" t="n"/>
       <c r="H53" s="27" t="n"/>
@@ -3072,10 +3244,14 @@
           <t>Không giảm</t>
         </is>
       </c>
-      <c r="B54" s="27" t="inlineStr"/>
-      <c r="C54" s="27" t="inlineStr"/>
-      <c r="D54" s="27" t="inlineStr"/>
-      <c r="E54" s="27" t="inlineStr"/>
+      <c r="B54" s="27" t="n"/>
+      <c r="C54" s="27" t="n"/>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F54" s="27" t="n"/>
       <c r="G54" s="27" t="n"/>
       <c r="H54" s="27" t="n"/>
@@ -3088,10 +3264,26 @@
           <t>Output</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr"/>
-      <c r="C55" s="8" t="inlineStr"/>
-      <c r="D55" s="8" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="F55" s="13" t="n"/>
       <c r="G55" s="13" t="n"/>
       <c r="H55" s="13" t="n"/>
@@ -3331,7 +3523,7 @@
     <row r="67">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>TC1:</t>
+          <t>TC1: Sinh nhật=T, tích điểm=T, voucher=T → Giảm 25% (ưu đãi cao nhất) (R1)</t>
         </is>
       </c>
       <c r="B67" s="24" t="n"/>
@@ -3347,7 +3539,7 @@
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>TC2:</t>
+          <t>TC2: Sinh nhật=T, tích điểm=T, voucher=F → Giảm 10% (R2)</t>
         </is>
       </c>
       <c r="B68" s="24" t="n"/>
@@ -3363,7 +3555,7 @@
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>TC3:</t>
+          <t>TC3: Sinh nhật=T, tích điểm=F, voucher=F → Giảm 5% (R3)</t>
         </is>
       </c>
       <c r="B69" s="24" t="n"/>
@@ -3379,7 +3571,7 @@
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>TC4:</t>
+          <t>TC4: Sinh nhật=F, tích điểm=F, voucher=T → Giảm 25% (R1)</t>
         </is>
       </c>
       <c r="B70" s="24" t="n"/>
@@ -3395,7 +3587,7 @@
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>TC5:</t>
+          <t>TC5: Sinh nhật=F, tích điểm=F, voucher=F → Không giảm (R4)</t>
         </is>
       </c>
       <c r="B71" s="24" t="n"/>
@@ -4151,14 +4343,30 @@
           <t>Giảm 15%</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr"/>
-      <c r="C36" s="27" t="inlineStr"/>
-      <c r="D36" s="27" t="inlineStr"/>
-      <c r="E36" s="27" t="inlineStr"/>
-      <c r="F36" s="27" t="inlineStr"/>
-      <c r="G36" s="27" t="inlineStr"/>
-      <c r="H36" s="27" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr"/>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
+      <c r="H36" s="27" t="n"/>
+      <c r="I36" s="27" t="n"/>
       <c r="J36" s="27" t="n"/>
     </row>
     <row r="37">
@@ -4167,14 +4375,30 @@
           <t>Giảm 10%</t>
         </is>
       </c>
-      <c r="B37" s="27" t="inlineStr"/>
-      <c r="C37" s="27" t="inlineStr"/>
-      <c r="D37" s="27" t="inlineStr"/>
-      <c r="E37" s="27" t="inlineStr"/>
-      <c r="F37" s="27" t="inlineStr"/>
-      <c r="G37" s="27" t="inlineStr"/>
-      <c r="H37" s="27" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr"/>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
       <c r="J37" s="27" t="n"/>
     </row>
     <row r="38">
@@ -4183,14 +4407,22 @@
           <t>Giảm 20%</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr"/>
-      <c r="C38" s="27" t="inlineStr"/>
-      <c r="D38" s="27" t="inlineStr"/>
-      <c r="E38" s="27" t="inlineStr"/>
-      <c r="F38" s="27" t="inlineStr"/>
-      <c r="G38" s="27" t="inlineStr"/>
-      <c r="H38" s="27" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr"/>
+      <c r="B38" s="27" t="n"/>
+      <c r="C38" s="27" t="n"/>
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G38" s="27" t="n"/>
+      <c r="H38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" s="27" t="n"/>
       <c r="J38" s="27" t="n"/>
     </row>
     <row r="39">
@@ -4199,14 +4431,18 @@
           <t>Không giảm / hoặc mức cộng dồn (tự ghi rõ)</t>
         </is>
       </c>
-      <c r="B39" s="27" t="inlineStr"/>
-      <c r="C39" s="27" t="inlineStr"/>
-      <c r="D39" s="27" t="inlineStr"/>
-      <c r="E39" s="27" t="inlineStr"/>
-      <c r="F39" s="27" t="inlineStr"/>
-      <c r="G39" s="27" t="inlineStr"/>
-      <c r="H39" s="27" t="inlineStr"/>
-      <c r="I39" s="27" t="inlineStr"/>
+      <c r="B39" s="27" t="n"/>
+      <c r="C39" s="27" t="n"/>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
+      <c r="H39" s="27" t="n"/>
+      <c r="I39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J39" s="27" t="n"/>
     </row>
     <row r="40">
@@ -4215,14 +4451,46 @@
           <t>Output</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="8" t="inlineStr"/>
-      <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="J40" s="13" t="n"/>
     </row>
     <row r="41">
@@ -4255,7 +4523,7 @@
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>Ghi quy tắc rút gọn theo đề (ưu đãi cao nhất / cộng dồn / ràng buộc không áp dụng...).</t>
+          <t>Quy tắc: Giảm giá được cộng dồn nếu áp dụng; phiếu 20% KHÔNG áp dụng khi KH mới (C1=T).</t>
         </is>
       </c>
       <c r="B43" s="24" t="n"/>
@@ -4321,8 +4589,16 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="13" t="n"/>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
       <c r="H46" s="13" t="n"/>
       <c r="I46" s="13" t="n"/>
       <c r="J46" s="13" t="n"/>
@@ -4335,26 +4611,34 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="13" t="n"/>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="H47" s="13" t="n"/>
       <c r="I47" s="13" t="n"/>
       <c r="J47" s="13" t="n"/>
@@ -4367,26 +4651,34 @@
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="13" t="n"/>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="H48" s="13" t="n"/>
       <c r="I48" s="13" t="n"/>
       <c r="J48" s="13" t="n"/>
@@ -4399,26 +4691,34 @@
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="13" t="n"/>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="H49" s="13" t="n"/>
       <c r="I49" s="13" t="n"/>
       <c r="J49" s="13" t="n"/>
@@ -4445,10 +4745,18 @@
           <t>Giảm 15%</t>
         </is>
       </c>
-      <c r="B51" s="27" t="inlineStr"/>
-      <c r="C51" s="27" t="inlineStr"/>
-      <c r="D51" s="27" t="inlineStr"/>
-      <c r="E51" s="27" t="inlineStr"/>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C51" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D51" s="27" t="n"/>
+      <c r="E51" s="27" t="n"/>
       <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
       <c r="H51" s="27" t="n"/>
@@ -4461,10 +4769,22 @@
           <t>Giảm 10%</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr"/>
-      <c r="C52" s="27" t="inlineStr"/>
-      <c r="D52" s="27" t="inlineStr"/>
-      <c r="E52" s="27" t="inlineStr"/>
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C52" s="27" t="n"/>
+      <c r="D52" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E52" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F52" s="27" t="n"/>
       <c r="G52" s="27" t="n"/>
       <c r="H52" s="27" t="n"/>
@@ -4477,11 +4797,19 @@
           <t>Giảm 20%</t>
         </is>
       </c>
-      <c r="B53" s="27" t="inlineStr"/>
-      <c r="C53" s="27" t="inlineStr"/>
-      <c r="D53" s="27" t="inlineStr"/>
-      <c r="E53" s="27" t="inlineStr"/>
-      <c r="F53" s="27" t="n"/>
+      <c r="B53" s="27" t="n"/>
+      <c r="C53" s="27" t="n"/>
+      <c r="D53" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E53" s="27" t="n"/>
+      <c r="F53" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="G53" s="27" t="n"/>
       <c r="H53" s="27" t="n"/>
       <c r="I53" s="27" t="n"/>
@@ -4493,12 +4821,16 @@
           <t>Không giảm / hoặc mức cộng dồn (tự ghi rõ)</t>
         </is>
       </c>
-      <c r="B54" s="27" t="inlineStr"/>
-      <c r="C54" s="27" t="inlineStr"/>
-      <c r="D54" s="27" t="inlineStr"/>
-      <c r="E54" s="27" t="inlineStr"/>
+      <c r="B54" s="27" t="n"/>
+      <c r="C54" s="27" t="n"/>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="n"/>
       <c r="F54" s="27" t="n"/>
-      <c r="G54" s="27" t="n"/>
+      <c r="G54" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H54" s="27" t="n"/>
       <c r="I54" s="27" t="n"/>
       <c r="J54" s="27" t="n"/>
@@ -4509,12 +4841,36 @@
           <t>Output</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr"/>
-      <c r="C55" s="8" t="inlineStr"/>
-      <c r="D55" s="8" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr"/>
-      <c r="F55" s="13" t="n"/>
-      <c r="G55" s="13" t="n"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="H55" s="13" t="n"/>
       <c r="I55" s="13" t="n"/>
       <c r="J55" s="13" t="n"/>
@@ -4752,7 +5108,7 @@
     <row r="67">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>TC1:</t>
+          <t>TC1: KH mới=T, loyalty=T, phiếu=T → Giảm 25% (15%+10%), phiếu không áp dụng (R1)</t>
         </is>
       </c>
       <c r="B67" s="24" t="n"/>
@@ -4768,7 +5124,7 @@
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>TC2:</t>
+          <t>TC2: KH mới=T, loyalty=F, phiếu=F → Giảm 15% (R2)</t>
         </is>
       </c>
       <c r="B68" s="24" t="n"/>
@@ -4784,7 +5140,7 @@
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>TC3:</t>
+          <t>TC3: KH mới=F, loyalty=T, phiếu=T → Giảm 30% (10%+20%) (R3)</t>
         </is>
       </c>
       <c r="B69" s="24" t="n"/>
@@ -4800,7 +5156,7 @@
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>TC4:</t>
+          <t>TC4: KH mới=F, loyalty=F, phiếu=T → Giảm 20% (R5)</t>
         </is>
       </c>
       <c r="B70" s="24" t="n"/>
@@ -4816,7 +5172,7 @@
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>TC5:</t>
+          <t>TC5: KH mới=F, loyalty=F, phiếu=F → Không giảm (R6)</t>
         </is>
       </c>
       <c r="B71" s="24" t="n"/>
@@ -4893,7 +5249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5077,7 +5433,7 @@
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>- Đơn hàng trong [100..500] (C2)</t>
+          <t>- Đơn hàng ≥ 100 (C2)</t>
         </is>
       </c>
       <c r="B12" s="24" t="n"/>
@@ -5107,6 +5463,11 @@
       <c r="J13" s="25" t="n"/>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>- Trả tiền mặt (C4)</t>
+        </is>
+      </c>
       <c r="B14" s="13" t="n"/>
       <c r="C14" s="13" t="n"/>
       <c r="D14" s="13" t="n"/>
@@ -5227,7 +5588,7 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>Do có 3 điều kiện đầu vào.</t>
+          <t>Do có 4 điều kiện đầu vào.</t>
         </is>
       </c>
       <c r="B22" s="24" t="n"/>
@@ -5243,7 +5604,7 @@
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>Tổng số rules = 2^3 = 8</t>
+          <t>Tổng số rules = 2^4 = 16</t>
         </is>
       </c>
       <c r="B23" s="24" t="n"/>
@@ -5286,7 +5647,7 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>Điều kiện 1: số lần thay đổi = 8 : 2 = 4  → 4T rồi 4F</t>
+          <t>Điều kiện 1: số lần thay đổi = 16 : 2 = 8  → 8T rồi 8F</t>
         </is>
       </c>
       <c r="B26" s="24" t="n"/>
@@ -5302,7 +5663,7 @@
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>Điều kiện 2: số lần thay đổi = 4 : 2 = 2  → TTFF lặp</t>
+          <t>Điều kiện 2: số lần thay đổi = 8 : 2 = 4  → 4T rồi 4F lặp</t>
         </is>
       </c>
       <c r="B27" s="24" t="n"/>
@@ -5318,7 +5679,7 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>Điều kiện 3: số lần thay đổi = 2 : 2 = 1  → T/F xen kẽ</t>
+          <t>Điều kiện 3: số lần thay đổi = 4 : 2 = 2  → TTFF lặp</t>
         </is>
       </c>
       <c r="B28" s="24" t="n"/>
@@ -5332,6 +5693,11 @@
       <c r="J28" s="25" t="n"/>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Điều kiện 4: số lần thay đổi = 2 : 2 = 1  → T/F xen kẽ</t>
+        </is>
+      </c>
       <c r="B29" s="13" t="n"/>
       <c r="C29" s="13" t="n"/>
       <c r="D29" s="13" t="n"/>
@@ -5404,7 +5770,46 @@
           <t>R8</t>
         </is>
       </c>
-      <c r="J31" s="13" t="n"/>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="N31" s="21" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="O31" s="21" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="P31" s="21" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="Q31" s="21" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
@@ -5434,30 +5839,69 @@
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="H32" s="22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="n"/>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L32" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="M32" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N32" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O32" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P32" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q32" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Đơn hàng trong [100..500] (C2)</t>
+          <t>Đơn hàng ≥ 100 (C2)</t>
         </is>
       </c>
       <c r="B33" s="22" t="inlineStr">
@@ -5472,22 +5916,22 @@
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H33" s="22" t="inlineStr">
@@ -5500,7 +5944,46 @@
           <t>F</t>
         </is>
       </c>
-      <c r="J33" s="13" t="n"/>
+      <c r="J33" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="K33" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="L33" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M33" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N33" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O33" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P33" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q33" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
@@ -5515,12 +5998,12 @@
       </c>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -5535,12 +6018,12 @@
       </c>
       <c r="G34" s="22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="H34" s="22" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
@@ -5548,12 +6031,51 @@
           <t>F</t>
         </is>
       </c>
-      <c r="J34" s="13" t="n"/>
+      <c r="J34" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="K34" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="L34" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="M34" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N34" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="O34" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="P34" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q34" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Hành động</t>
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>Trả tiền mặt (C4)</t>
         </is>
       </c>
       <c r="B35" s="24" t="n"/>
@@ -5564,119 +6086,318 @@
       <c r="G35" s="24" t="n"/>
       <c r="H35" s="24" t="n"/>
       <c r="I35" s="25" t="n"/>
-      <c r="J35" s="13" t="n"/>
+      <c r="J35" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L35" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M35" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N35" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="O35" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P35" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="Q35" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>Ship 0$</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr"/>
-      <c r="C36" s="27" t="inlineStr"/>
-      <c r="D36" s="27" t="inlineStr"/>
-      <c r="E36" s="27" t="inlineStr"/>
-      <c r="F36" s="27" t="inlineStr"/>
-      <c r="G36" s="27" t="inlineStr"/>
-      <c r="H36" s="27" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr"/>
-      <c r="J36" s="27" t="n"/>
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Hành động</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="25" t="n"/>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="25" t="n"/>
+      <c r="L36" s="25" t="n"/>
+      <c r="M36" s="25" t="n"/>
+      <c r="N36" s="25" t="n"/>
+      <c r="O36" s="25" t="n"/>
+      <c r="P36" s="25" t="n"/>
+      <c r="Q36" s="25" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>Ship 5$</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="inlineStr"/>
-      <c r="C37" s="27" t="inlineStr"/>
-      <c r="D37" s="27" t="inlineStr"/>
-      <c r="E37" s="27" t="inlineStr"/>
-      <c r="F37" s="27" t="inlineStr"/>
-      <c r="G37" s="27" t="inlineStr"/>
-      <c r="H37" s="27" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr"/>
-      <c r="J37" s="27" t="n"/>
+          <t>Ship 0$</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
+      <c r="J37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" s="27" t="n"/>
+      <c r="L37" s="27" t="n"/>
+      <c r="M37" s="27" t="n"/>
+      <c r="N37" s="27" t="n"/>
+      <c r="O37" s="27" t="n"/>
+      <c r="P37" s="27" t="n"/>
+      <c r="Q37" s="27" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>Ship 10$</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="inlineStr"/>
-      <c r="C38" s="27" t="inlineStr"/>
-      <c r="D38" s="27" t="inlineStr"/>
-      <c r="E38" s="27" t="inlineStr"/>
-      <c r="F38" s="27" t="inlineStr"/>
-      <c r="G38" s="27" t="inlineStr"/>
-      <c r="H38" s="27" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr"/>
+          <t>Ship 5$</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="n"/>
+      <c r="C38" s="27" t="n"/>
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="27" t="n"/>
+      <c r="G38" s="27" t="n"/>
+      <c r="H38" s="27" t="n"/>
+      <c r="I38" s="27" t="n"/>
       <c r="J38" s="27" t="n"/>
+      <c r="K38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" s="27" t="n"/>
+      <c r="M38" s="27" t="n"/>
+      <c r="N38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" s="27" t="n"/>
+      <c r="P38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q38" s="27" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
         <is>
+          <t>Ship 10$</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="n"/>
+      <c r="C39" s="27" t="n"/>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
+      <c r="H39" s="27" t="n"/>
+      <c r="I39" s="27" t="n"/>
+      <c r="J39" s="27" t="n"/>
+      <c r="K39" s="27" t="n"/>
+      <c r="L39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N39" s="27" t="n"/>
+      <c r="O39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" s="27" t="n"/>
+      <c r="Q39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
           <t>Khác (tự điền nếu phát sinh)</t>
         </is>
       </c>
-      <c r="B39" s="27" t="inlineStr"/>
-      <c r="C39" s="27" t="inlineStr"/>
-      <c r="D39" s="27" t="inlineStr"/>
-      <c r="E39" s="27" t="inlineStr"/>
-      <c r="F39" s="27" t="inlineStr"/>
-      <c r="G39" s="27" t="inlineStr"/>
-      <c r="H39" s="27" t="inlineStr"/>
-      <c r="I39" s="27" t="inlineStr"/>
-      <c r="J39" s="27" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="B40" s="27" t="n"/>
+      <c r="C40" s="27" t="n"/>
+      <c r="D40" s="27" t="n"/>
+      <c r="E40" s="27" t="n"/>
+      <c r="F40" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G40" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H40" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" s="27" t="n"/>
+      <c r="K40" s="27" t="n"/>
+      <c r="L40" s="27" t="n"/>
+      <c r="M40" s="27" t="n"/>
+      <c r="N40" s="27" t="n"/>
+      <c r="O40" s="27" t="n"/>
+      <c r="P40" s="27" t="n"/>
+      <c r="Q40" s="27" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="8" t="inlineStr"/>
-      <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr"/>
-      <c r="J40" s="13" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="13" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="13" t="n"/>
-      <c r="J41" s="13" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>0$</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>0$</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>0$</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>0$</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>0$</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>5$</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>10$</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t>10$</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>5$</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>10$</t>
+        </is>
+      </c>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
+          <t>5$</t>
+        </is>
+      </c>
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t>10$</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>BƯỚC 4: RÚT GỌN BẢNG QUYẾT ĐỊNH</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="n"/>
-      <c r="C42" s="24" t="n"/>
-      <c r="D42" s="24" t="n"/>
-      <c r="E42" s="24" t="n"/>
-      <c r="F42" s="24" t="n"/>
-      <c r="G42" s="24" t="n"/>
-      <c r="H42" s="24" t="n"/>
-      <c r="I42" s="24" t="n"/>
-      <c r="J42" s="25" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>Ghi quy tắc rút gọn theo đề (ưu đãi cao nhất / cộng dồn / ràng buộc không áp dụng...).</t>
         </is>
       </c>
       <c r="B43" s="24" t="n"/>
@@ -5690,92 +6411,74 @@
       <c r="J43" s="25" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-      <c r="I44" s="13" t="n"/>
-      <c r="J44" s="13" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Quy tắc: Dựa trên giá trị đơn hàng (&gt;=500 / 100–499 / &lt;100), KH thân thiết và trả tiền mặt để tính phí ship như đề; các kết hợp logic không thể xảy ra (VD: C1=T nhưng C2=F) đánh dấu 'Khác'.</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="n"/>
+      <c r="C44" s="24" t="n"/>
+      <c r="D44" s="24" t="n"/>
+      <c r="E44" s="24" t="n"/>
+      <c r="F44" s="24" t="n"/>
+      <c r="G44" s="24" t="n"/>
+      <c r="H44" s="24" t="n"/>
+      <c r="I44" s="24" t="n"/>
+      <c r="J44" s="25" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>Bảng sau rút gọn: (tự chọn các rule đại diện, đổi tên cột R1,R2,... nếu cần)</t>
         </is>
       </c>
-      <c r="B45" s="24" t="n"/>
-      <c r="C45" s="24" t="n"/>
-      <c r="D45" s="24" t="n"/>
-      <c r="E45" s="24" t="n"/>
-      <c r="F45" s="24" t="n"/>
-      <c r="G45" s="24" t="n"/>
-      <c r="H45" s="24" t="n"/>
-      <c r="I45" s="24" t="n"/>
-      <c r="J45" s="25" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="B46" s="24" t="n"/>
+      <c r="C46" s="24" t="n"/>
+      <c r="D46" s="24" t="n"/>
+      <c r="E46" s="24" t="n"/>
+      <c r="F46" s="24" t="n"/>
+      <c r="G46" s="24" t="n"/>
+      <c r="H46" s="24" t="n"/>
+      <c r="I46" s="24" t="n"/>
+      <c r="J46" s="25" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>Điều kiện</t>
         </is>
       </c>
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="C46" s="21" t="inlineStr">
+      <c r="C47" s="21" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="D46" s="21" t="inlineStr">
+      <c r="D47" s="21" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="E46" s="21" t="inlineStr">
+      <c r="E47" s="21" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="13" t="n"/>
-      <c r="H46" s="13" t="n"/>
-      <c r="I46" s="13" t="n"/>
-      <c r="J46" s="13" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>Đơn hàng ≥ 500 (C1)</t>
-        </is>
-      </c>
-      <c r="B47" s="22" t="inlineStr">
-        <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="C47" s="22" t="inlineStr">
-        <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="D47" s="22" t="inlineStr">
-        <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="E47" s="22" t="inlineStr">
-        <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="13" t="n"/>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
       <c r="H47" s="13" t="n"/>
       <c r="I47" s="13" t="n"/>
       <c r="J47" s="13" t="n"/>
@@ -5783,31 +6486,39 @@
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>Đơn hàng trong [100..500] (C2)</t>
+          <t>Đơn hàng ≥ 500 (C1)</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="13" t="n"/>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="H48" s="13" t="n"/>
       <c r="I48" s="13" t="n"/>
       <c r="J48" s="13" t="n"/>
@@ -5815,93 +6526,141 @@
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>KH thân thiết (C3)</t>
+          <t>Đơn hàng ≥ 100 (C2)</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="13" t="n"/>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="H49" s="13" t="n"/>
       <c r="I49" s="13" t="n"/>
       <c r="J49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>Hành động</t>
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>KH thân thiết (C3)</t>
         </is>
       </c>
       <c r="B50" s="24" t="n"/>
       <c r="C50" s="24" t="n"/>
       <c r="D50" s="24" t="n"/>
       <c r="E50" s="25" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="13" t="n"/>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H50" s="13" t="n"/>
       <c r="I50" s="13" t="n"/>
       <c r="J50" s="13" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="26" t="inlineStr">
-        <is>
-          <t>Ship 0$</t>
-        </is>
-      </c>
-      <c r="B51" s="27" t="inlineStr"/>
-      <c r="C51" s="27" t="inlineStr"/>
-      <c r="D51" s="27" t="inlineStr"/>
-      <c r="E51" s="27" t="inlineStr"/>
-      <c r="F51" s="27" t="n"/>
-      <c r="G51" s="27" t="n"/>
-      <c r="H51" s="27" t="n"/>
-      <c r="I51" s="27" t="n"/>
-      <c r="J51" s="27" t="n"/>
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>Trả tiền mặt (C4)</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="n"/>
+      <c r="I51" s="13" t="n"/>
+      <c r="J51" s="13" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="inlineStr">
-        <is>
-          <t>Ship 5$</t>
-        </is>
-      </c>
-      <c r="B52" s="27" t="inlineStr"/>
-      <c r="C52" s="27" t="inlineStr"/>
-      <c r="D52" s="27" t="inlineStr"/>
-      <c r="E52" s="27" t="inlineStr"/>
-      <c r="F52" s="27" t="n"/>
-      <c r="G52" s="27" t="n"/>
-      <c r="H52" s="27" t="n"/>
-      <c r="I52" s="27" t="n"/>
-      <c r="J52" s="27" t="n"/>
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>Hành động</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="n"/>
+      <c r="C52" s="24" t="n"/>
+      <c r="D52" s="24" t="n"/>
+      <c r="E52" s="25" t="n"/>
+      <c r="F52" s="25" t="n"/>
+      <c r="G52" s="25" t="n"/>
+      <c r="H52" s="13" t="n"/>
+      <c r="I52" s="13" t="n"/>
+      <c r="J52" s="13" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="26" t="inlineStr">
         <is>
-          <t>Ship 10$</t>
-        </is>
-      </c>
-      <c r="B53" s="27" t="inlineStr"/>
-      <c r="C53" s="27" t="inlineStr"/>
-      <c r="D53" s="27" t="inlineStr"/>
-      <c r="E53" s="27" t="inlineStr"/>
+          <t>Ship 0$</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C53" s="27" t="n"/>
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F53" s="27" t="n"/>
       <c r="G53" s="27" t="n"/>
       <c r="H53" s="27" t="n"/>
@@ -5911,173 +6670,170 @@
     <row r="54">
       <c r="A54" s="26" t="inlineStr">
         <is>
-          <t>Khác (tự điền nếu phát sinh)</t>
-        </is>
-      </c>
-      <c r="B54" s="27" t="inlineStr"/>
-      <c r="C54" s="27" t="inlineStr"/>
-      <c r="D54" s="27" t="inlineStr"/>
-      <c r="E54" s="27" t="inlineStr"/>
+          <t>Ship 5$</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="n"/>
+      <c r="C54" s="27" t="n"/>
+      <c r="D54" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E54" s="27" t="n"/>
       <c r="F54" s="27" t="n"/>
-      <c r="G54" s="27" t="n"/>
+      <c r="G54" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="H54" s="27" t="n"/>
       <c r="I54" s="27" t="n"/>
       <c r="J54" s="27" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>Ship 10$</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="n"/>
+      <c r="C55" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D55" s="27" t="n"/>
+      <c r="E55" s="27" t="n"/>
+      <c r="F55" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G55" s="27" t="n"/>
+      <c r="H55" s="27" t="n"/>
+      <c r="I55" s="27" t="n"/>
+      <c r="J55" s="27" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>Khác (tự điền nếu phát sinh)</t>
+        </is>
+      </c>
+      <c r="B56" s="27" t="n"/>
+      <c r="C56" s="27" t="n"/>
+      <c r="D56" s="27" t="n"/>
+      <c r="E56" s="27" t="n"/>
+      <c r="F56" s="27" t="n"/>
+      <c r="G56" s="27" t="n"/>
+      <c r="H56" s="27" t="n"/>
+      <c r="I56" s="27" t="n"/>
+      <c r="J56" s="27" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr"/>
-      <c r="C55" s="8" t="inlineStr"/>
-      <c r="D55" s="8" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr"/>
-      <c r="F55" s="13" t="n"/>
-      <c r="G55" s="13" t="n"/>
-      <c r="H55" s="13" t="n"/>
-      <c r="I55" s="13" t="n"/>
-      <c r="J55" s="13" t="n"/>
-    </row>
-    <row r="56">
-      <c r="B56" s="13" t="n"/>
-      <c r="C56" s="13" t="n"/>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
-      <c r="G56" s="13" t="n"/>
-      <c r="H56" s="13" t="n"/>
-      <c r="I56" s="13" t="n"/>
-      <c r="J56" s="13" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>PHÂN VÙNG TƯƠNG ĐƯƠNG + GIÁ TRỊ BIÊN (EP + BVA)</t>
-        </is>
-      </c>
-      <c r="B57" s="24" t="n"/>
-      <c r="C57" s="24" t="n"/>
-      <c r="D57" s="24" t="n"/>
-      <c r="E57" s="24" t="n"/>
-      <c r="F57" s="24" t="n"/>
-      <c r="G57" s="24" t="n"/>
-      <c r="H57" s="24" t="n"/>
-      <c r="I57" s="24" t="n"/>
-      <c r="J57" s="25" t="n"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0$</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>10$</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>5$</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0$</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>10$</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>5$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="21" t="inlineStr">
-        <is>
-          <t>Tham số</t>
-        </is>
-      </c>
-      <c r="B58" s="21" t="inlineStr">
-        <is>
-          <t>EP hợp lệ</t>
-        </is>
-      </c>
-      <c r="C58" s="21" t="inlineStr">
-        <is>
-          <t>EP không hợp lệ</t>
-        </is>
-      </c>
-      <c r="D58" s="21" t="inlineStr">
-        <is>
-          <t>Biên dưới</t>
-        </is>
-      </c>
-      <c r="E58" s="21" t="inlineStr">
-        <is>
-          <t>Dưới biên</t>
-        </is>
-      </c>
-      <c r="F58" s="21" t="inlineStr">
-        <is>
-          <t>Trên biên</t>
-        </is>
-      </c>
-      <c r="G58" s="21" t="inlineStr">
-        <is>
-          <t>Biên trên</t>
-        </is>
-      </c>
-      <c r="H58" s="21" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="13" t="n"/>
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="13" t="n"/>
+      <c r="H58" s="13" t="n"/>
       <c r="I58" s="13" t="n"/>
       <c r="J58" s="13" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="15" t="inlineStr">
-        <is>
-          <t>Giá trị đơn hàng</t>
-        </is>
-      </c>
-      <c r="B59" s="22" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="C59" s="22" t="inlineStr">
-        <is>
-          <t>≤0 / không phải số</t>
-        </is>
-      </c>
-      <c r="D59" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E59" s="22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F59" s="22" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr"/>
-      <c r="H59" s="22" t="inlineStr">
-        <is>
-          <t>Mốc biên: 100 và 500</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n"/>
-      <c r="J59" s="13" t="n"/>
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>PHÂN VÙNG TƯƠNG ĐƯƠNG + GIÁ TRỊ BIÊN (EP + BVA)</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="n"/>
+      <c r="C59" s="24" t="n"/>
+      <c r="D59" s="24" t="n"/>
+      <c r="E59" s="24" t="n"/>
+      <c r="F59" s="24" t="n"/>
+      <c r="G59" s="24" t="n"/>
+      <c r="H59" s="24" t="n"/>
+      <c r="I59" s="24" t="n"/>
+      <c r="J59" s="25" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>Mốc 100</t>
-        </is>
-      </c>
-      <c r="B60" s="22" t="inlineStr">
-        <is>
-          <t>99/100/101</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr"/>
-      <c r="D60" s="22" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr"/>
-      <c r="F60" s="22" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr"/>
-      <c r="H60" s="22" t="inlineStr">
-        <is>
-          <t>BVA quanh 100</t>
+      <c r="A60" s="21" t="inlineStr">
+        <is>
+          <t>Tham số</t>
+        </is>
+      </c>
+      <c r="B60" s="21" t="inlineStr">
+        <is>
+          <t>EP hợp lệ</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="inlineStr">
+        <is>
+          <t>EP không hợp lệ</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="inlineStr">
+        <is>
+          <t>Biên dưới</t>
+        </is>
+      </c>
+      <c r="E60" s="21" t="inlineStr">
+        <is>
+          <t>Dưới biên</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="inlineStr">
+        <is>
+          <t>Trên biên</t>
+        </is>
+      </c>
+      <c r="G60" s="21" t="inlineStr">
+        <is>
+          <t>Biên trên</t>
+        </is>
+      </c>
+      <c r="H60" s="21" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
         </is>
       </c>
       <c r="I60" s="13" t="n"/>
@@ -6086,30 +6842,38 @@
     <row r="61">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t>Mốc 500</t>
+          <t>Giá trị đơn hàng</t>
         </is>
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>499/500/501</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr"/>
+          <t>&gt;0</t>
+        </is>
+      </c>
+      <c r="C61" s="22" t="inlineStr">
+        <is>
+          <t>≤0 / không phải số</t>
+        </is>
+      </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E61" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F61" s="22" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr"/>
       <c r="H61" s="22" t="inlineStr">
         <is>
-          <t>BVA quanh 500</t>
+          <t>Mốc biên: 100 và 500</t>
         </is>
       </c>
       <c r="I61" s="13" t="n"/>
@@ -6118,26 +6882,30 @@
     <row r="62">
       <c r="A62" s="15" t="inlineStr">
         <is>
-          <t>Trả tiền mặt</t>
+          <t>Mốc 100</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>{T,F}</t>
-        </is>
-      </c>
-      <c r="C62" s="22" t="inlineStr">
-        <is>
-          <t>null/sai kiểu</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr"/>
+          <t>99/100/101</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr"/>
+      <c r="D62" s="22" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="inlineStr"/>
-      <c r="F62" s="8" t="inlineStr"/>
+      <c r="F62" s="22" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
       <c r="G62" s="8" t="inlineStr"/>
       <c r="H62" s="22" t="inlineStr">
         <is>
-          <t>Ảnh hưởng phí ship theo đề</t>
+          <t>BVA quanh 100</t>
         </is>
       </c>
       <c r="I62" s="13" t="n"/>
@@ -6146,50 +6914,83 @@
     <row r="63">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t>[thêm]</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr"/>
+          <t>Mốc 500</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>499/500/501</t>
+        </is>
+      </c>
       <c r="C63" s="8" t="inlineStr"/>
-      <c r="D63" s="8" t="inlineStr"/>
+      <c r="D63" s="22" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="inlineStr"/>
-      <c r="F63" s="8" t="inlineStr"/>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
       <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="8" t="inlineStr"/>
+      <c r="H63" s="22" t="inlineStr">
+        <is>
+          <t>BVA quanh 500</t>
+        </is>
+      </c>
       <c r="I63" s="13" t="n"/>
       <c r="J63" s="13" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="15" t="inlineStr">
         <is>
-          <t>[thêm]</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr"/>
-      <c r="C64" s="8" t="inlineStr"/>
+          <t>Trả tiền mặt</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>{T,F}</t>
+        </is>
+      </c>
+      <c r="C64" s="22" t="inlineStr">
+        <is>
+          <t>null/sai kiểu</t>
+        </is>
+      </c>
       <c r="D64" s="8" t="inlineStr"/>
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="8" t="inlineStr"/>
       <c r="G64" s="8" t="inlineStr"/>
-      <c r="H64" s="8" t="inlineStr"/>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t>Ảnh hưởng phí ship theo đề</t>
+        </is>
+      </c>
       <c r="I64" s="13" t="n"/>
       <c r="J64" s="13" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="13" t="n"/>
-      <c r="C65" s="13" t="n"/>
-      <c r="D65" s="13" t="n"/>
-      <c r="E65" s="13" t="n"/>
-      <c r="F65" s="13" t="n"/>
-      <c r="G65" s="13" t="n"/>
-      <c r="H65" s="13" t="n"/>
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>[thêm]</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr"/>
+      <c r="C65" s="8" t="inlineStr"/>
+      <c r="D65" s="8" t="inlineStr"/>
+      <c r="E65" s="8" t="inlineStr"/>
+      <c r="F65" s="8" t="inlineStr"/>
+      <c r="G65" s="8" t="inlineStr"/>
+      <c r="H65" s="8" t="inlineStr"/>
       <c r="I65" s="13" t="n"/>
       <c r="J65" s="13" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>THIẾT KẾ TEST CASE (từ Decision Table + EP/BVA)</t>
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>[thêm]</t>
         </is>
       </c>
       <c r="B66" s="24" t="n"/>
@@ -6202,26 +7003,11 @@
       <c r="I66" s="24" t="n"/>
       <c r="J66" s="25" t="n"/>
     </row>
-    <row r="67">
-      <c r="A67" s="15" t="inlineStr">
-        <is>
-          <t>Gợi ý viết 1 dòng (giống ảnh): TC1: [điều kiện...] → [kết quả...](R?)</t>
-        </is>
-      </c>
-      <c r="B67" s="24" t="n"/>
-      <c r="C67" s="24" t="n"/>
-      <c r="D67" s="24" t="n"/>
-      <c r="E67" s="24" t="n"/>
-      <c r="F67" s="24" t="n"/>
-      <c r="G67" s="24" t="n"/>
-      <c r="H67" s="24" t="n"/>
-      <c r="I67" s="24" t="n"/>
-      <c r="J67" s="25" t="n"/>
-    </row>
+    <row r="67"/>
     <row r="68">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t>TC1:</t>
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>THIẾT KẾ TEST CASE (từ Decision Table + EP/BVA)</t>
         </is>
       </c>
       <c r="B68" s="24" t="n"/>
@@ -6232,12 +7018,19 @@
       <c r="G68" s="24" t="n"/>
       <c r="H68" s="24" t="n"/>
       <c r="I68" s="24" t="n"/>
-      <c r="J68" s="25" t="n"/>
+      <c r="J68" s="24" t="n"/>
+      <c r="K68" s="24" t="n"/>
+      <c r="L68" s="24" t="n"/>
+      <c r="M68" s="24" t="n"/>
+      <c r="N68" s="24" t="n"/>
+      <c r="O68" s="24" t="n"/>
+      <c r="P68" s="24" t="n"/>
+      <c r="Q68" s="25" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>TC2:</t>
+          <t>Gợi ý viết 1 dòng (giống ảnh): TC1: [điều kiện...] → [kết quả...](R?)</t>
         </is>
       </c>
       <c r="B69" s="24" t="n"/>
@@ -6248,12 +7041,19 @@
       <c r="G69" s="24" t="n"/>
       <c r="H69" s="24" t="n"/>
       <c r="I69" s="24" t="n"/>
-      <c r="J69" s="25" t="n"/>
+      <c r="J69" s="24" t="n"/>
+      <c r="K69" s="24" t="n"/>
+      <c r="L69" s="24" t="n"/>
+      <c r="M69" s="24" t="n"/>
+      <c r="N69" s="24" t="n"/>
+      <c r="O69" s="24" t="n"/>
+      <c r="P69" s="24" t="n"/>
+      <c r="Q69" s="25" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>TC3:</t>
+          <t>TC1: Order=500, loyal=F, cash=F → Ship 0$ (R1)</t>
         </is>
       </c>
       <c r="B70" s="24" t="n"/>
@@ -6264,12 +7064,19 @@
       <c r="G70" s="24" t="n"/>
       <c r="H70" s="24" t="n"/>
       <c r="I70" s="24" t="n"/>
-      <c r="J70" s="25" t="n"/>
+      <c r="J70" s="24" t="n"/>
+      <c r="K70" s="24" t="n"/>
+      <c r="L70" s="24" t="n"/>
+      <c r="M70" s="24" t="n"/>
+      <c r="N70" s="24" t="n"/>
+      <c r="O70" s="24" t="n"/>
+      <c r="P70" s="24" t="n"/>
+      <c r="Q70" s="25" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>TC4:</t>
+          <t>TC2: Order=100, loyal=F, cash=F → Ship 10$ (R2)</t>
         </is>
       </c>
       <c r="B71" s="24" t="n"/>
@@ -6280,12 +7087,19 @@
       <c r="G71" s="24" t="n"/>
       <c r="H71" s="24" t="n"/>
       <c r="I71" s="24" t="n"/>
-      <c r="J71" s="25" t="n"/>
+      <c r="J71" s="24" t="n"/>
+      <c r="K71" s="24" t="n"/>
+      <c r="L71" s="24" t="n"/>
+      <c r="M71" s="24" t="n"/>
+      <c r="N71" s="24" t="n"/>
+      <c r="O71" s="24" t="n"/>
+      <c r="P71" s="24" t="n"/>
+      <c r="Q71" s="25" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t>TC5:</t>
+          <t>TC3: Order=100, loyal=T, cash=F → Ship 5$ (R3)</t>
         </is>
       </c>
       <c r="B72" s="24" t="n"/>
@@ -6296,36 +7110,91 @@
       <c r="G72" s="24" t="n"/>
       <c r="H72" s="24" t="n"/>
       <c r="I72" s="24" t="n"/>
-      <c r="J72" s="25" t="n"/>
+      <c r="J72" s="24" t="n"/>
+      <c r="K72" s="24" t="n"/>
+      <c r="L72" s="24" t="n"/>
+      <c r="M72" s="24" t="n"/>
+      <c r="N72" s="24" t="n"/>
+      <c r="O72" s="24" t="n"/>
+      <c r="P72" s="24" t="n"/>
+      <c r="Q72" s="25" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>TC4: Order=100, loyal=T, cash=T → Ship 0$ (R4)</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="n"/>
+      <c r="C73" s="24" t="n"/>
+      <c r="D73" s="24" t="n"/>
+      <c r="E73" s="24" t="n"/>
+      <c r="F73" s="24" t="n"/>
+      <c r="G73" s="24" t="n"/>
+      <c r="H73" s="24" t="n"/>
+      <c r="I73" s="24" t="n"/>
+      <c r="J73" s="24" t="n"/>
+      <c r="K73" s="24" t="n"/>
+      <c r="L73" s="24" t="n"/>
+      <c r="M73" s="24" t="n"/>
+      <c r="N73" s="24" t="n"/>
+      <c r="O73" s="24" t="n"/>
+      <c r="P73" s="24" t="n"/>
+      <c r="Q73" s="25" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>TC5: Order=99, loyal=F, cash=T → Ship 5$ (R6)</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="n"/>
+      <c r="C74" s="24" t="n"/>
+      <c r="D74" s="24" t="n"/>
+      <c r="E74" s="24" t="n"/>
+      <c r="F74" s="24" t="n"/>
+      <c r="G74" s="24" t="n"/>
+      <c r="H74" s="24" t="n"/>
+      <c r="I74" s="24" t="n"/>
+      <c r="J74" s="24" t="n"/>
+      <c r="K74" s="24" t="n"/>
+      <c r="L74" s="24" t="n"/>
+      <c r="M74" s="24" t="n"/>
+      <c r="N74" s="24" t="n"/>
+      <c r="O74" s="24" t="n"/>
+      <c r="P74" s="24" t="n"/>
+      <c r="Q74" s="25" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="39">
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A73:Q73"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A72:J72"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A70:Q70"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A67:J67"/>
+    <mergeCell ref="A69:Q69"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A59:J59"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A11:J11"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A45:J45"/>
     <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A74:Q74"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A69:J69"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A71:Q71"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A18:J18"/>
@@ -6333,10 +7202,10 @@
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A72:Q72"/>
     <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A68:Q68"/>
     <mergeCell ref="A42:J42"/>
-    <mergeCell ref="A71:J71"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="B32 B33 B34 C32 C33 C34 D32 D33 D34 E32 E33 E34 F32 F33 F34 G32 G33 G34 H32 H33 H34 I32 I33 I34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -7041,14 +7910,22 @@
           <t>Phí 500$</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr"/>
-      <c r="C36" s="27" t="inlineStr"/>
-      <c r="D36" s="27" t="inlineStr"/>
-      <c r="E36" s="27" t="inlineStr"/>
-      <c r="F36" s="27" t="inlineStr"/>
-      <c r="G36" s="27" t="inlineStr"/>
-      <c r="H36" s="27" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr"/>
+      <c r="B36" s="27" t="n"/>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
+      <c r="H36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J36" s="27" t="n"/>
     </row>
     <row r="37">
@@ -7057,14 +7934,18 @@
           <t>Phí 1000$</t>
         </is>
       </c>
-      <c r="B37" s="27" t="inlineStr"/>
-      <c r="C37" s="27" t="inlineStr"/>
-      <c r="D37" s="27" t="inlineStr"/>
-      <c r="E37" s="27" t="inlineStr"/>
-      <c r="F37" s="27" t="inlineStr"/>
-      <c r="G37" s="27" t="inlineStr"/>
-      <c r="H37" s="27" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr"/>
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
       <c r="J37" s="27" t="n"/>
     </row>
     <row r="38">
@@ -7073,14 +7954,30 @@
           <t>Phí 1500$</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr"/>
-      <c r="C38" s="27" t="inlineStr"/>
-      <c r="D38" s="27" t="inlineStr"/>
-      <c r="E38" s="27" t="inlineStr"/>
-      <c r="F38" s="27" t="inlineStr"/>
-      <c r="G38" s="27" t="inlineStr"/>
-      <c r="H38" s="27" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr"/>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="n"/>
+      <c r="I38" s="27" t="n"/>
       <c r="J38" s="27" t="n"/>
     </row>
     <row r="39">
@@ -7089,14 +7986,18 @@
           <t>Phí 3000$</t>
         </is>
       </c>
-      <c r="B39" s="27" t="inlineStr"/>
-      <c r="C39" s="27" t="inlineStr"/>
-      <c r="D39" s="27" t="inlineStr"/>
-      <c r="E39" s="27" t="inlineStr"/>
-      <c r="F39" s="27" t="inlineStr"/>
-      <c r="G39" s="27" t="inlineStr"/>
-      <c r="H39" s="27" t="inlineStr"/>
-      <c r="I39" s="27" t="inlineStr"/>
+      <c r="B39" s="27" t="n"/>
+      <c r="C39" s="27" t="n"/>
+      <c r="D39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
+      <c r="H39" s="27" t="n"/>
+      <c r="I39" s="27" t="n"/>
       <c r="J39" s="27" t="n"/>
     </row>
     <row r="40">
@@ -7105,14 +8006,46 @@
           <t>Output</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="8" t="inlineStr"/>
-      <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>1500$</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>1500$</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>3000$</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>1000$</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>1500$</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>1500$</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>500$</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>500$</t>
+        </is>
+      </c>
       <c r="J40" s="13" t="n"/>
     </row>
     <row r="41">
@@ -7145,7 +8078,7 @@
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>Ghi quy tắc rút gọn theo đề (ưu đãi cao nhất / cộng dồn / ràng buộc không áp dụng...).</t>
+          <t>Quy tắc: Nếu tuổi ≥ 65 → phí 1500$ (ưu tiên, không phụ thuộc giới tính). Nếu tuổi &lt; 65: Nữ → 500$; Nam &amp; tuổi &lt; 25 → 3000$; Nam &amp; tuổi 25–64 → 1000$.</t>
         </is>
       </c>
       <c r="B43" s="24" t="n"/>
@@ -7225,22 +8158,22 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F47" s="13" t="n"/>
@@ -7257,22 +8190,22 @@
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F48" s="13" t="n"/>
@@ -7289,22 +8222,22 @@
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F49" s="13" t="n"/>
@@ -7335,10 +8268,14 @@
           <t>Phí 500$</t>
         </is>
       </c>
-      <c r="B51" s="27" t="inlineStr"/>
-      <c r="C51" s="27" t="inlineStr"/>
-      <c r="D51" s="27" t="inlineStr"/>
-      <c r="E51" s="27" t="inlineStr"/>
+      <c r="B51" s="27" t="n"/>
+      <c r="C51" s="27" t="n"/>
+      <c r="D51" s="27" t="n"/>
+      <c r="E51" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
       <c r="H51" s="27" t="n"/>
@@ -7351,10 +8288,14 @@
           <t>Phí 1000$</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr"/>
-      <c r="C52" s="27" t="inlineStr"/>
-      <c r="D52" s="27" t="inlineStr"/>
-      <c r="E52" s="27" t="inlineStr"/>
+      <c r="B52" s="27" t="n"/>
+      <c r="C52" s="27" t="n"/>
+      <c r="D52" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E52" s="27" t="n"/>
       <c r="F52" s="27" t="n"/>
       <c r="G52" s="27" t="n"/>
       <c r="H52" s="27" t="n"/>
@@ -7367,10 +8308,14 @@
           <t>Phí 1500$</t>
         </is>
       </c>
-      <c r="B53" s="27" t="inlineStr"/>
-      <c r="C53" s="27" t="inlineStr"/>
-      <c r="D53" s="27" t="inlineStr"/>
-      <c r="E53" s="27" t="inlineStr"/>
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C53" s="27" t="n"/>
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="27" t="n"/>
       <c r="F53" s="27" t="n"/>
       <c r="G53" s="27" t="n"/>
       <c r="H53" s="27" t="n"/>
@@ -7383,10 +8328,14 @@
           <t>Phí 3000$</t>
         </is>
       </c>
-      <c r="B54" s="27" t="inlineStr"/>
-      <c r="C54" s="27" t="inlineStr"/>
-      <c r="D54" s="27" t="inlineStr"/>
-      <c r="E54" s="27" t="inlineStr"/>
+      <c r="B54" s="27" t="n"/>
+      <c r="C54" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="n"/>
       <c r="F54" s="27" t="n"/>
       <c r="G54" s="27" t="n"/>
       <c r="H54" s="27" t="n"/>
@@ -7399,10 +8348,26 @@
           <t>Output</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr"/>
-      <c r="C55" s="8" t="inlineStr"/>
-      <c r="D55" s="8" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>1500$</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>3000$</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>1000$</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>500$</t>
+        </is>
+      </c>
       <c r="F55" s="13" t="n"/>
       <c r="G55" s="13" t="n"/>
       <c r="H55" s="13" t="n"/>
@@ -7694,7 +8659,7 @@
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>TC1:</t>
+          <t>TC1: Nam, tuổi=65 → Phí 1500$ (biên 65) (R1)</t>
         </is>
       </c>
       <c r="B68" s="24" t="n"/>
@@ -7710,7 +8675,7 @@
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>TC2:</t>
+          <t>TC2: Nam, tuổi=24 → Phí 3000$ (dưới biên 25) (R2)</t>
         </is>
       </c>
       <c r="B69" s="24" t="n"/>
@@ -7726,7 +8691,7 @@
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>TC3:</t>
+          <t>TC3: Nam, tuổi=25 → Phí 1000$ (tại biên 25) (R3)</t>
         </is>
       </c>
       <c r="B70" s="24" t="n"/>
@@ -7742,7 +8707,7 @@
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>TC4:</t>
+          <t>TC4: Nữ, tuổi=64 → Phí 500$ (dưới biên 65) (R4)</t>
         </is>
       </c>
       <c r="B71" s="24" t="n"/>
@@ -7758,7 +8723,7 @@
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t>TC5:</t>
+          <t>TC5: Nữ, tuổi=66 → Phí 1500$ (trên biên 65) (R1)</t>
         </is>
       </c>
       <c r="B72" s="24" t="n"/>
@@ -8514,14 +9479,18 @@
           <t>Loại A</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr"/>
-      <c r="C36" s="27" t="inlineStr"/>
-      <c r="D36" s="27" t="inlineStr"/>
-      <c r="E36" s="27" t="inlineStr"/>
-      <c r="F36" s="27" t="inlineStr"/>
-      <c r="G36" s="27" t="inlineStr"/>
-      <c r="H36" s="27" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr"/>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
+      <c r="H36" s="27" t="n"/>
+      <c r="I36" s="27" t="n"/>
       <c r="J36" s="27" t="n"/>
     </row>
     <row r="37">
@@ -8530,14 +9499,18 @@
           <t>Loại B</t>
         </is>
       </c>
-      <c r="B37" s="27" t="inlineStr"/>
-      <c r="C37" s="27" t="inlineStr"/>
-      <c r="D37" s="27" t="inlineStr"/>
-      <c r="E37" s="27" t="inlineStr"/>
-      <c r="F37" s="27" t="inlineStr"/>
-      <c r="G37" s="27" t="inlineStr"/>
-      <c r="H37" s="27" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr"/>
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
       <c r="J37" s="27" t="n"/>
     </row>
     <row r="38">
@@ -8546,14 +9519,18 @@
           <t>Loại C</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr"/>
-      <c r="C38" s="27" t="inlineStr"/>
-      <c r="D38" s="27" t="inlineStr"/>
-      <c r="E38" s="27" t="inlineStr"/>
-      <c r="F38" s="27" t="inlineStr"/>
-      <c r="G38" s="27" t="inlineStr"/>
-      <c r="H38" s="27" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr"/>
+      <c r="B38" s="27" t="n"/>
+      <c r="C38" s="27" t="n"/>
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="27" t="n"/>
+      <c r="G38" s="27" t="n"/>
+      <c r="H38" s="27" t="n"/>
+      <c r="I38" s="27" t="n"/>
       <c r="J38" s="27" t="n"/>
     </row>
     <row r="39">
@@ -8562,14 +9539,34 @@
           <t>Không mở TK</t>
         </is>
       </c>
-      <c r="B39" s="27" t="inlineStr"/>
-      <c r="C39" s="27" t="inlineStr"/>
-      <c r="D39" s="27" t="inlineStr"/>
-      <c r="E39" s="27" t="inlineStr"/>
-      <c r="F39" s="27" t="inlineStr"/>
-      <c r="G39" s="27" t="inlineStr"/>
-      <c r="H39" s="27" t="inlineStr"/>
-      <c r="I39" s="27" t="inlineStr"/>
+      <c r="B39" s="27" t="n"/>
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J39" s="27" t="n"/>
     </row>
     <row r="40">
@@ -8578,14 +9575,46 @@
           <t>Output</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="8" t="inlineStr"/>
-      <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="J40" s="13" t="n"/>
     </row>
     <row r="41">
@@ -8618,7 +9647,7 @@
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>Ghi quy tắc rút gọn theo đề (ưu đãi cao nhất / cộng dồn / ràng buộc không áp dụng...).</t>
+          <t>Quy tắc: Nếu hồ sơ không hợp lệ (C3=F) → không mở TK (ưu tiên). Nếu hồ sơ hợp lệ: phân loại theo tuổi (≥21) và tiền gửi (≥100): A/B/C; riêng &lt;21 &amp; &lt;100 → không mở TK.</t>
         </is>
       </c>
       <c r="B43" s="24" t="n"/>
@@ -8684,7 +9713,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="F46" s="13" t="n"/>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
       <c r="G46" s="13" t="n"/>
       <c r="H46" s="13" t="n"/>
       <c r="I46" s="13" t="n"/>
@@ -8698,25 +9731,29 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E47" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="F47" s="13" t="n"/>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="G47" s="13" t="n"/>
       <c r="H47" s="13" t="n"/>
       <c r="I47" s="13" t="n"/>
@@ -8730,25 +9767,29 @@
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="F48" s="13" t="n"/>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="G48" s="13" t="n"/>
       <c r="H48" s="13" t="n"/>
       <c r="I48" s="13" t="n"/>
@@ -8762,25 +9803,29 @@
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E49" s="22" t="inlineStr">
         <is>
-          <t>[T/F/-]</t>
-        </is>
-      </c>
-      <c r="F49" s="13" t="n"/>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
       <c r="G49" s="13" t="n"/>
       <c r="H49" s="13" t="n"/>
       <c r="I49" s="13" t="n"/>
@@ -8808,10 +9853,14 @@
           <t>Loại A</t>
         </is>
       </c>
-      <c r="B51" s="27" t="inlineStr"/>
-      <c r="C51" s="27" t="inlineStr"/>
-      <c r="D51" s="27" t="inlineStr"/>
-      <c r="E51" s="27" t="inlineStr"/>
+      <c r="B51" s="27" t="n"/>
+      <c r="C51" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D51" s="27" t="n"/>
+      <c r="E51" s="27" t="n"/>
       <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
       <c r="H51" s="27" t="n"/>
@@ -8824,10 +9873,14 @@
           <t>Loại B</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr"/>
-      <c r="C52" s="27" t="inlineStr"/>
-      <c r="D52" s="27" t="inlineStr"/>
-      <c r="E52" s="27" t="inlineStr"/>
+      <c r="B52" s="27" t="n"/>
+      <c r="C52" s="27" t="n"/>
+      <c r="D52" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E52" s="27" t="n"/>
       <c r="F52" s="27" t="n"/>
       <c r="G52" s="27" t="n"/>
       <c r="H52" s="27" t="n"/>
@@ -8840,10 +9893,14 @@
           <t>Loại C</t>
         </is>
       </c>
-      <c r="B53" s="27" t="inlineStr"/>
-      <c r="C53" s="27" t="inlineStr"/>
-      <c r="D53" s="27" t="inlineStr"/>
-      <c r="E53" s="27" t="inlineStr"/>
+      <c r="B53" s="27" t="n"/>
+      <c r="C53" s="27" t="n"/>
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F53" s="27" t="n"/>
       <c r="G53" s="27" t="n"/>
       <c r="H53" s="27" t="n"/>
@@ -8856,11 +9913,19 @@
           <t>Không mở TK</t>
         </is>
       </c>
-      <c r="B54" s="27" t="inlineStr"/>
-      <c r="C54" s="27" t="inlineStr"/>
-      <c r="D54" s="27" t="inlineStr"/>
-      <c r="E54" s="27" t="inlineStr"/>
-      <c r="F54" s="27" t="n"/>
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C54" s="27" t="n"/>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="n"/>
+      <c r="F54" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="G54" s="27" t="n"/>
       <c r="H54" s="27" t="n"/>
       <c r="I54" s="27" t="n"/>
@@ -8872,11 +9937,31 @@
           <t>Output</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr"/>
-      <c r="C55" s="8" t="inlineStr"/>
-      <c r="D55" s="8" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr"/>
-      <c r="F55" s="13" t="n"/>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="G55" s="13" t="n"/>
       <c r="H55" s="13" t="n"/>
       <c r="I55" s="13" t="n"/>
@@ -9175,7 +10260,7 @@
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>TC1:</t>
+          <t>TC1: Hồ sơ hợp lệ=T, tuổi=21, tiền gửi=100 → TK loại A (biên 21 &amp; 100) (R2)</t>
         </is>
       </c>
       <c r="B68" s="24" t="n"/>
@@ -9191,7 +10276,7 @@
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>TC2:</t>
+          <t>TC2: Hồ sơ hợp lệ=T, tuổi=20, tiền gửi=100 → TK loại B (dưới biên 21) (R3)</t>
         </is>
       </c>
       <c r="B69" s="24" t="n"/>
@@ -9207,7 +10292,7 @@
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>TC3:</t>
+          <t>TC3: Hồ sơ hợp lệ=T, tuổi=21, tiền gửi=99 → TK loại C (dưới biên 100) (R4)</t>
         </is>
       </c>
       <c r="B70" s="24" t="n"/>
@@ -9223,7 +10308,7 @@
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>TC4:</t>
+          <t>TC4: Hồ sơ hợp lệ=T, tuổi=20, tiền gửi=99 → Không mở TK (R5)</t>
         </is>
       </c>
       <c r="B71" s="24" t="n"/>
@@ -9239,7 +10324,7 @@
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t>TC5:</t>
+          <t>TC5: Hồ sơ hợp lệ=F, tuổi=21, tiền gửi=100 → Không mở TK (ưu tiên hồ sơ) (R1)</t>
         </is>
       </c>
       <c r="B72" s="24" t="n"/>
